--- a/lab.xlsx
+++ b/lab.xlsx
@@ -345,7 +345,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,6 +531,79 @@
       </c>
       <c r="U2">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>46316.33562179398</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46316.33628800926</v>
+      </c>
+      <c r="C3" s="1">
+        <v>46315</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ee.kobotoolbox.org:Uwhrmqi2VK0M3pFo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Flavio Santos</t>
+        </is>
+      </c>
+      <c r="F3" s="1">
+        <v>46316</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BRO-2610210800-2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Íntegra</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M3">
+        <v>898094358</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>e2fbfa25-8cdf-493b-b15f-919970526758</t>
+        </is>
+      </c>
+      <c r="O3" s="1">
+        <v>46316.46128472222</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>fhsantos</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>vqKeMJpZNeGJkfQ4RvmFXb</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>uuid:e2fbfa25-8cdf-493b-b15f-919970526758</t>
+        </is>
+      </c>
+      <c r="U3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -540,7 +613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -844,6 +917,73 @@
       <c r="S4" t="inlineStr">
         <is>
           <t>uuid:e5f2d3d5-57ed-4973-bf53-7a4a7fa4c5dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Culex sp.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Larva</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Negativo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Análise Laboratorial de Amostras</t>
+        </is>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>898094358</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>e2fbfa25-8cdf-493b-b15f-919970526758</t>
+        </is>
+      </c>
+      <c r="N5" s="1">
+        <v>46316.46128472222</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>fhsantos</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>vqKeMJpZNeGJkfQ4RvmFXb</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>uuid:e2fbfa25-8cdf-493b-b15f-919970526758</t>
         </is>
       </c>
     </row>

--- a/lab.xlsx
+++ b/lab.xlsx
@@ -345,7 +345,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -604,6 +604,79 @@
       </c>
       <c r="U3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>46316.40097542824</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46316.40174317129</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46315</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ee.kobotoolbox.org:Uwhrmqi2VK0M3pFo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Flavio Santos</t>
+        </is>
+      </c>
+      <c r="F4" s="1">
+        <v>46316</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BRO-2610210934-3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Íntegra</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M4">
+        <v>898171234</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>61af9ada-480b-4c13-8710-5b4ba451124a</t>
+        </is>
+      </c>
+      <c r="O4" s="1">
+        <v>46316.52673611111</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>fhsantos</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>vqKeMJpZNeGJkfQ4RvmFXb</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>uuid:61af9ada-480b-4c13-8710-5b4ba451124a</t>
+        </is>
+      </c>
+      <c r="U4">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +686,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -984,6 +1057,140 @@
       <c r="S5" t="inlineStr">
         <is>
           <t>uuid:e2fbfa25-8cdf-493b-b15f-919970526758</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aedes aegypti</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Larva</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Análise Laboratorial de Amostras</t>
+        </is>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>898171234</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>61af9ada-480b-4c13-8710-5b4ba451124a</t>
+        </is>
+      </c>
+      <c r="N6" s="1">
+        <v>46316.52673611111</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>fhsantos</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>vqKeMJpZNeGJkfQ4RvmFXb</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>uuid:61af9ada-480b-4c13-8710-5b4ba451124a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Culex sp.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Larva</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Negativo</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Análise Laboratorial de Amostras</t>
+        </is>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>898171234</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>61af9ada-480b-4c13-8710-5b4ba451124a</t>
+        </is>
+      </c>
+      <c r="N7" s="1">
+        <v>46316.52673611111</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>fhsantos</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>vqKeMJpZNeGJkfQ4RvmFXb</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>uuid:61af9ada-480b-4c13-8710-5b4ba451124a</t>
         </is>
       </c>
     </row>
